--- a/templates/SH_Project_Report_Template_v4.xlsx
+++ b/templates/SH_Project_Report_Template_v4.xlsx
@@ -1729,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="18">
-        <f>IF(A13="","",IFERROR(REPT("\u2588",ROUND(C13*25,0)),""))</f>
+        <f>IF(A13="","",IFERROR(REPT("█",ROUND(C13*25,0)),""))</f>
         <v>0</v>
       </c>
       <c r="F13" s="6" t="s">
@@ -1756,7 +1756,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="22">
-        <f>IF(A14="","",IFERROR(REPT("\u2588",ROUND(C14*25,0)),""))</f>
+        <f>IF(A14="","",IFERROR(REPT("█",ROUND(C14*25,0)),""))</f>
         <v>0</v>
       </c>
       <c r="F14" s="6" t="s">
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="18">
-        <f>IF(A15="","",IFERROR(REPT("\u2588",ROUND(C15*25,0)),""))</f>
+        <f>IF(A15="","",IFERROR(REPT("█",ROUND(C15*25,0)),""))</f>
         <v>0</v>
       </c>
       <c r="F15" s="6" t="s">
@@ -1810,7 +1810,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="22">
-        <f>IF(A16="","",IFERROR(REPT("\u2588",ROUND(C16*25,0)),""))</f>
+        <f>IF(A16="","",IFERROR(REPT("█",ROUND(C16*25,0)),""))</f>
         <v>0</v>
       </c>
       <c r="F16" s="6" t="s">
@@ -1837,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="18">
-        <f>IF(A17="","",IFERROR(REPT("\u2588",ROUND(C17*25,0)),""))</f>
+        <f>IF(A17="","",IFERROR(REPT("█",ROUND(C17*25,0)),""))</f>
         <v>0</v>
       </c>
       <c r="F17" s="6" t="s">
@@ -1864,7 +1864,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="22">
-        <f>IF(A18="","",IFERROR(REPT("\u2588",ROUND(C18*25,0)),""))</f>
+        <f>IF(A18="","",IFERROR(REPT("█",ROUND(C18*25,0)),""))</f>
         <v>0</v>
       </c>
       <c r="F18" s="6" t="s">
@@ -1891,7 +1891,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="18">
-        <f>IF(A19="","",IFERROR(REPT("\u2588",ROUND(C19*25,0)),""))</f>
+        <f>IF(A19="","",IFERROR(REPT("█",ROUND(C19*25,0)),""))</f>
         <v>0</v>
       </c>
       <c r="F19" s="6" t="s">
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="22">
-        <f>IF(A20="","",IFERROR(REPT("\u2588",ROUND(C20*25,0)),""))</f>
+        <f>IF(A20="","",IFERROR(REPT("█",ROUND(C20*25,0)),""))</f>
         <v>0</v>
       </c>
       <c r="F20" s="6" t="s">
@@ -1945,7 +1945,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="18">
-        <f>IF(A21="","",IFERROR(REPT("\u2588",ROUND(C21*25,0)),""))</f>
+        <f>IF(A21="","",IFERROR(REPT("█",ROUND(C21*25,0)),""))</f>
         <v>0</v>
       </c>
       <c r="F21" s="6" t="s">
@@ -1972,7 +1972,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="22">
-        <f>IF(A22="","",IFERROR(REPT("\u2588",ROUND(C22*25,0)),""))</f>
+        <f>IF(A22="","",IFERROR(REPT("█",ROUND(C22*25,0)),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="18">
-        <f>IF(A23="","",IFERROR(REPT("\u2588",ROUND(C23*25,0)),""))</f>
+        <f>IF(A23="","",IFERROR(REPT("█",ROUND(C23*25,0)),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="22">
-        <f>IF(A24="","",IFERROR(REPT("\u2588",ROUND(C24*25,0)),""))</f>
+        <f>IF(A24="","",IFERROR(REPT("█",ROUND(C24*25,0)),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="18">
-        <f>IF(A25="","",IFERROR(REPT("\u2588",ROUND(C25*25,0)),""))</f>
+        <f>IF(A25="","",IFERROR(REPT("█",ROUND(C25*25,0)),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="22">
-        <f>IF(A26="","",IFERROR(REPT("\u2588",ROUND(C26*25,0)),""))</f>
+        <f>IF(A26="","",IFERROR(REPT("█",ROUND(C26*25,0)),""))</f>
         <v>0</v>
       </c>
       <c r="F26" s="33" t="s">
@@ -2069,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="18">
-        <f>IF(A27="","",IFERROR(REPT("\u2588",ROUND(C27*25,0)),""))</f>
+        <f>IF(A27="","",IFERROR(REPT("█",ROUND(C27*25,0)),""))</f>
         <v>0</v>
       </c>
       <c r="F27" s="14" t="s">
@@ -2098,7 +2098,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="22">
-        <f>IF(A28="","",IFERROR(REPT("\u2588",ROUND(C28*25,0)),""))</f>
+        <f>IF(A28="","",IFERROR(REPT("█",ROUND(C28*25,0)),""))</f>
         <v>0</v>
       </c>
       <c r="F28" s="4" t="s">
@@ -2129,7 +2129,7 @@
         <v>0</v>
       </c>
       <c r="D29" s="18">
-        <f>IF(A29="","",IFERROR(REPT("\u2588",ROUND(C29*25,0)),""))</f>
+        <f>IF(A29="","",IFERROR(REPT("█",ROUND(C29*25,0)),""))</f>
         <v>0</v>
       </c>
       <c r="F29" s="3" t="s">
@@ -2160,7 +2160,7 @@
         <v>0</v>
       </c>
       <c r="D30" s="22">
-        <f>IF(A30="","",IFERROR(REPT("\u2588",ROUND(C30*25,0)),""))</f>
+        <f>IF(A30="","",IFERROR(REPT("█",ROUND(C30*25,0)),""))</f>
         <v>0</v>
       </c>
       <c r="F30" s="4" t="s">
@@ -2191,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="18">
-        <f>IF(A31="","",IFERROR(REPT("\u2588",ROUND(C31*25,0)),""))</f>
+        <f>IF(A31="","",IFERROR(REPT("█",ROUND(C31*25,0)),""))</f>
         <v>0</v>
       </c>
       <c r="F31" s="3" t="s">
@@ -2222,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="22">
-        <f>IF(A32="","",IFERROR(REPT("\u2588",ROUND(C32*25,0)),""))</f>
+        <f>IF(A32="","",IFERROR(REPT("█",ROUND(C32*25,0)),""))</f>
         <v>0</v>
       </c>
       <c r="F32" s="4" t="s">
@@ -2253,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="D33" s="18">
-        <f>IF(A33="","",IFERROR(REPT("\u2588",ROUND(C33*25,0)),""))</f>
+        <f>IF(A33="","",IFERROR(REPT("█",ROUND(C33*25,0)),""))</f>
         <v>0</v>
       </c>
       <c r="F33" s="3" t="s">
@@ -2284,7 +2284,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="22">
-        <f>IF(A34="","",IFERROR(REPT("\u2588",ROUND(C34*25,0)),""))</f>
+        <f>IF(A34="","",IFERROR(REPT("█",ROUND(C34*25,0)),""))</f>
         <v>0</v>
       </c>
       <c r="F34" s="4" t="s">
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="18">
-        <f>IF(A35="","",IFERROR(REPT("\u2588",ROUND(C35*25,0)),""))</f>
+        <f>IF(A35="","",IFERROR(REPT("█",ROUND(C35*25,0)),""))</f>
         <v>0</v>
       </c>
       <c r="F35" s="3" t="s">
@@ -2346,7 +2346,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="22">
-        <f>IF(A36="","",IFERROR(REPT("\u2588",ROUND(C36*25,0)),""))</f>
+        <f>IF(A36="","",IFERROR(REPT("█",ROUND(C36*25,0)),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="D37" s="18">
-        <f>IF(A37="","",IFERROR(REPT("\u2588",ROUND(C37*25,0)),""))</f>
+        <f>IF(A37="","",IFERROR(REPT("█",ROUND(C37*25,0)),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="22">
-        <f>IF(A38="","",IFERROR(REPT("\u2588",ROUND(C38*25,0)),""))</f>
+        <f>IF(A38="","",IFERROR(REPT("█",ROUND(C38*25,0)),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="18">
-        <f>IF(A39="","",IFERROR(REPT("\u2588",ROUND(C39*25,0)),""))</f>
+        <f>IF(A39="","",IFERROR(REPT("█",ROUND(C39*25,0)),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="22">
-        <f>IF(A40="","",IFERROR(REPT("\u2588",ROUND(C40*25,0)),""))</f>
+        <f>IF(A40="","",IFERROR(REPT("█",ROUND(C40*25,0)),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="18">
-        <f>IF(A41="","",IFERROR(REPT("\u2588",ROUND(C41*25,0)),""))</f>
+        <f>IF(A41="","",IFERROR(REPT("█",ROUND(C41*25,0)),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
         <v>0</v>
       </c>
       <c r="D42" s="22">
-        <f>IF(A42="","",IFERROR(REPT("\u2588",ROUND(C42*25,0)),""))</f>
+        <f>IF(A42="","",IFERROR(REPT("█",ROUND(C42*25,0)),""))</f>
         <v>0</v>
       </c>
     </row>

--- a/templates/SH_Project_Report_Template_v4.xlsx
+++ b/templates/SH_Project_Report_Template_v4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AmberShamim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A9839C-769E-4B4F-9BCF-AB14154BA255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01FBE4A7-73A0-4E0D-B268-6FD2002E4A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Data" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Dashboard" sheetId="3" r:id="rId3"/>
     <sheet name="Template Guide" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -261,9 +261,6 @@
     <t>Not Specified</t>
   </si>
   <si>
-    <t>Sheffield Haworth  ·  Confidential  ·  Generated via Ezekia Document Generator</t>
-  </si>
-  <si>
     <t>TEMPLATE GUIDE — Sheffield Haworth Project Report</t>
   </si>
   <si>
@@ -322,6 +319,9 @@
   </si>
   <si>
     <t>Dashboard pipeline table has 30 rows — blank rows hide automatically when tag is empty.</t>
+  </si>
+  <si>
+    <t>Sheffield Haworth  ·  Confidential  ·  Generated via DocGen</t>
   </si>
 </sst>
 </file>
@@ -344,125 +344,125 @@
       <sz val="8"/>
       <color rgb="FF6B6B6B"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="8"/>
       <color rgb="FFAAAAAA"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF888888"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="22"/>
       <color rgb="FFC8A96E"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="6"/>
       <color rgb="FFC8A96E"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="28"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFC8A96E"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF1A1A2E"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF2C2C2C"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF2C2C2C"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF6B6B6B"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="7"/>
       <color rgb="FFC8A96E"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF6B6B6B"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="3"/>
       <color rgb="FFC8A96E"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFC8A96E"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF888888"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -484,7 +484,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -537,6 +537,18 @@
       <patternFill patternType="solid">
         <fgColor theme="3" tint="-0.249977111117893"/>
         <bgColor rgb="FF1A1A2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor rgb="FF16213E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="-0.249977111117893"/>
+        <bgColor rgb="FF16213E"/>
       </patternFill>
     </fill>
   </fills>
@@ -597,34 +609,7 @@
   </cellStyleXfs>
   <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -674,24 +659,51 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1035,58 +1047,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" hidden="1">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="25.5" customHeight="1">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="36" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G2"/>
+  <autoFilter ref="A2:G2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -1098,13 +1110,13 @@
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1551,1091 +1563,1047 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A1" s="8" t="e" vm="1">
+      <c r="A1" s="30" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
     </row>
     <row r="2" spans="1:10" ht="21.75" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
     </row>
     <row r="3" spans="1:10" ht="3" customHeight="1">
-      <c r="A3" s="31"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
     </row>
     <row r="4" spans="1:10" ht="7.5" customHeight="1"/>
     <row r="5" spans="1:10" ht="18" customHeight="1">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35" t="s">
+      <c r="B5" s="33"/>
+      <c r="C5" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35" t="s">
+      <c r="D5" s="33"/>
+      <c r="E5" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35" t="s">
+      <c r="F5" s="33"/>
+      <c r="G5" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35" t="s">
+      <c r="H5" s="33"/>
+      <c r="I5" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="35"/>
+      <c r="J5" s="33"/>
     </row>
     <row r="6" spans="1:10" ht="21.75" customHeight="1">
-      <c r="A6" s="7">
+      <c r="A6" s="29">
         <f>COUNTA('Project Data'!$A$3:$A$10000)</f>
         <v>0</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7">
+      <c r="B6" s="29"/>
+      <c r="C6" s="29">
         <f>COUNTIF(_Pivot!B2:B31,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7">
+      <c r="D6" s="29"/>
+      <c r="E6" s="29">
         <f>COUNTIF('Project Data'!$E$3:$E$10000,"*Interview*")</f>
         <v>0</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7">
+      <c r="F6" s="29"/>
+      <c r="G6" s="29">
         <f>COUNTIF('Project Data'!$E$3:$E$10000,"*Offer*")</f>
         <v>0</v>
       </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7">
+      <c r="H6" s="29"/>
+      <c r="I6" s="29">
         <f>COUNTIF('Project Data'!$E$3:$E$10000,"*Placed*")</f>
         <v>0</v>
       </c>
-      <c r="J6" s="7"/>
+      <c r="J6" s="29"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
+      <c r="A8" s="29"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
     </row>
     <row r="9" spans="1:10" ht="3.75" customHeight="1">
-      <c r="A9" s="32"/>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" spans="1:10" ht="9.75" customHeight="1"/>
     <row r="11" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="F11" s="33" t="s">
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="F11" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
     </row>
     <row r="12" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="6"/>
-      <c r="H12" s="5" t="s">
+      <c r="G12" s="26"/>
+      <c r="H12" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="15">
+      <c r="A13" s="6">
         <f>IF(_Pivot!A2="","",_Pivot!A2)</f>
         <v>0</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="7">
         <f>IF(A13="","",_Pivot!B2)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="8">
         <f>IF(A13="","",_Pivot!C2)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="18">
-        <f>IF(A13="","",IFERROR(REPT("█",ROUND(C13*25,0)),""))</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="6" t="s">
+      <c r="D13" s="9">
+        <f t="shared" ref="D13:D42" si="0">IF(A13="","",IFERROR(REPT("█",ROUND(C13*25,0)),""))</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="5" t="s">
+      <c r="G13" s="26"/>
+      <c r="H13" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="19">
+      <c r="A14" s="10">
         <f>IF(_Pivot!A3="","",_Pivot!A3)</f>
         <v>0</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="11">
         <f>IF(A14="","",_Pivot!B3)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="12">
         <f>IF(A14="","",_Pivot!C3)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="22">
-        <f>IF(A14="","",IFERROR(REPT("█",ROUND(C14*25,0)),""))</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="6" t="s">
+      <c r="D14" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="5" t="s">
+      <c r="G14" s="26"/>
+      <c r="H14" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="15">
+      <c r="A15" s="6">
         <f>IF(_Pivot!A4="","",_Pivot!A4)</f>
         <v>0</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="7">
         <f>IF(A15="","",_Pivot!B4)</f>
         <v>0</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="8">
         <f>IF(A15="","",_Pivot!C4)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="18">
-        <f>IF(A15="","",IFERROR(REPT("█",ROUND(C15*25,0)),""))</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="6" t="s">
+      <c r="D15" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="5" t="s">
+      <c r="G15" s="26"/>
+      <c r="H15" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="19">
+      <c r="A16" s="10">
         <f>IF(_Pivot!A5="","",_Pivot!A5)</f>
         <v>0</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="11">
         <f>IF(A16="","",_Pivot!B5)</f>
         <v>0</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="12">
         <f>IF(A16="","",_Pivot!C5)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="22">
-        <f>IF(A16="","",IFERROR(REPT("█",ROUND(C16*25,0)),""))</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="6" t="s">
+      <c r="D16" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="G16" s="6"/>
-      <c r="H16" s="5" t="s">
+      <c r="G16" s="26"/>
+      <c r="H16" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="15">
+      <c r="A17" s="6">
         <f>IF(_Pivot!A6="","",_Pivot!A6)</f>
         <v>0</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="7">
         <f>IF(A17="","",_Pivot!B6)</f>
         <v>0</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="8">
         <f>IF(A17="","",_Pivot!C6)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="18">
-        <f>IF(A17="","",IFERROR(REPT("█",ROUND(C17*25,0)),""))</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="6" t="s">
+      <c r="D17" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="5" t="s">
+      <c r="G17" s="26"/>
+      <c r="H17" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="19">
+      <c r="A18" s="10">
         <f>IF(_Pivot!A7="","",_Pivot!A7)</f>
         <v>0</v>
       </c>
-      <c r="B18" s="20">
+      <c r="B18" s="11">
         <f>IF(A18="","",_Pivot!B7)</f>
         <v>0</v>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="12">
         <f>IF(A18="","",_Pivot!C7)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="22">
-        <f>IF(A18="","",IFERROR(REPT("█",ROUND(C18*25,0)),""))</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="6" t="s">
+      <c r="D18" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="G18" s="6"/>
-      <c r="H18" s="5" t="s">
+      <c r="G18" s="26"/>
+      <c r="H18" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="27"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="15">
+      <c r="A19" s="6">
         <f>IF(_Pivot!A8="","",_Pivot!A8)</f>
         <v>0</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="7">
         <f>IF(A19="","",_Pivot!B8)</f>
         <v>0</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="8">
         <f>IF(A19="","",_Pivot!C8)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="18">
-        <f>IF(A19="","",IFERROR(REPT("█",ROUND(C19*25,0)),""))</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="6" t="s">
+      <c r="D19" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="5" t="s">
+      <c r="G19" s="26"/>
+      <c r="H19" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="19">
+      <c r="A20" s="10">
         <f>IF(_Pivot!A9="","",_Pivot!A9)</f>
         <v>0</v>
       </c>
-      <c r="B20" s="20">
+      <c r="B20" s="11">
         <f>IF(A20="","",_Pivot!B9)</f>
         <v>0</v>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="12">
         <f>IF(A20="","",_Pivot!C9)</f>
         <v>0</v>
       </c>
-      <c r="D20" s="22">
-        <f>IF(A20="","",IFERROR(REPT("█",ROUND(C20*25,0)),""))</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="6" t="s">
+      <c r="D20" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="G20" s="6"/>
-      <c r="H20" s="5" t="s">
+      <c r="G20" s="26"/>
+      <c r="H20" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="15">
+      <c r="A21" s="6">
         <f>IF(_Pivot!A10="","",_Pivot!A10)</f>
         <v>0</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="7">
         <f>IF(A21="","",_Pivot!B10)</f>
         <v>0</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="8">
         <f>IF(A21="","",_Pivot!C10)</f>
         <v>0</v>
       </c>
-      <c r="D21" s="18">
-        <f>IF(A21="","",IFERROR(REPT("█",ROUND(C21*25,0)),""))</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="6" t="s">
+      <c r="D21" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="G21" s="6"/>
-      <c r="H21" s="5" t="s">
+      <c r="G21" s="26"/>
+      <c r="H21" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27"/>
     </row>
     <row r="22" spans="1:10" ht="18" customHeight="1">
-      <c r="A22" s="19">
+      <c r="A22" s="10">
         <f>IF(_Pivot!A11="","",_Pivot!A11)</f>
         <v>0</v>
       </c>
-      <c r="B22" s="20">
+      <c r="B22" s="11">
         <f>IF(A22="","",_Pivot!B11)</f>
         <v>0</v>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="12">
         <f>IF(A22="","",_Pivot!C11)</f>
         <v>0</v>
       </c>
-      <c r="D22" s="22">
-        <f>IF(A22="","",IFERROR(REPT("█",ROUND(C22*25,0)),""))</f>
+      <c r="D22" s="13">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="18" customHeight="1">
-      <c r="A23" s="15">
+      <c r="A23" s="6">
         <f>IF(_Pivot!A12="","",_Pivot!A12)</f>
         <v>0</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="7">
         <f>IF(A23="","",_Pivot!B12)</f>
         <v>0</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="8">
         <f>IF(A23="","",_Pivot!C12)</f>
         <v>0</v>
       </c>
-      <c r="D23" s="18">
-        <f>IF(A23="","",IFERROR(REPT("█",ROUND(C23*25,0)),""))</f>
+      <c r="D23" s="9">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="18" customHeight="1">
-      <c r="A24" s="19">
+      <c r="A24" s="10">
         <f>IF(_Pivot!A13="","",_Pivot!A13)</f>
         <v>0</v>
       </c>
-      <c r="B24" s="20">
+      <c r="B24" s="11">
         <f>IF(A24="","",_Pivot!B13)</f>
         <v>0</v>
       </c>
-      <c r="C24" s="21">
+      <c r="C24" s="12">
         <f>IF(A24="","",_Pivot!C13)</f>
         <v>0</v>
       </c>
-      <c r="D24" s="22">
-        <f>IF(A24="","",IFERROR(REPT("█",ROUND(C24*25,0)),""))</f>
+      <c r="D24" s="13">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="18" customHeight="1">
-      <c r="A25" s="15">
+      <c r="A25" s="6">
         <f>IF(_Pivot!A14="","",_Pivot!A14)</f>
         <v>0</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="7">
         <f>IF(A25="","",_Pivot!B14)</f>
         <v>0</v>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="8">
         <f>IF(A25="","",_Pivot!C14)</f>
         <v>0</v>
       </c>
-      <c r="D25" s="18">
-        <f>IF(A25="","",IFERROR(REPT("█",ROUND(C25*25,0)),""))</f>
+      <c r="D25" s="9">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="19">
+      <c r="A26" s="10">
         <f>IF(_Pivot!A15="","",_Pivot!A15)</f>
         <v>0</v>
       </c>
-      <c r="B26" s="20">
+      <c r="B26" s="11">
         <f>IF(A26="","",_Pivot!B15)</f>
         <v>0</v>
       </c>
-      <c r="C26" s="21">
+      <c r="C26" s="12">
         <f>IF(A26="","",_Pivot!C15)</f>
         <v>0</v>
       </c>
-      <c r="D26" s="22">
-        <f>IF(A26="","",IFERROR(REPT("█",ROUND(C26*25,0)),""))</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="33" t="s">
+      <c r="D26" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="24"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="15">
+      <c r="A27" s="6">
         <f>IF(_Pivot!A16="","",_Pivot!A16)</f>
         <v>0</v>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="7">
         <f>IF(A27="","",_Pivot!B16)</f>
         <v>0</v>
       </c>
-      <c r="C27" s="17">
+      <c r="C27" s="8">
         <f>IF(A27="","",_Pivot!C16)</f>
         <v>0</v>
       </c>
-      <c r="D27" s="18">
-        <f>IF(A27="","",IFERROR(REPT("█",ROUND(C27*25,0)),""))</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="14" t="s">
+      <c r="D27" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14" t="s">
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J27" s="14" t="s">
+      <c r="J27" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="18" customHeight="1">
-      <c r="A28" s="19">
+      <c r="A28" s="10">
         <f>IF(_Pivot!A17="","",_Pivot!A17)</f>
         <v>0</v>
       </c>
-      <c r="B28" s="20">
+      <c r="B28" s="11">
         <f>IF(A28="","",_Pivot!B17)</f>
         <v>0</v>
       </c>
-      <c r="C28" s="21">
+      <c r="C28" s="12">
         <f>IF(A28="","",_Pivot!C17)</f>
         <v>0</v>
       </c>
-      <c r="D28" s="22">
-        <f>IF(A28="","",IFERROR(REPT("█",ROUND(C28*25,0)),""))</f>
-        <v>0</v>
-      </c>
-      <c r="F28" s="4" t="s">
+      <c r="D28" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="16">
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="7">
         <f>IF(F28="","",COUNTIF('Project Data'!$D$3:$D$10000,F28))</f>
         <v>0</v>
       </c>
-      <c r="J28" s="17">
-        <f>IFERROR(I28/SUM($I$28:$I$35),"")</f>
+      <c r="J28" s="8">
+        <f t="shared" ref="J28:J35" si="1">IFERROR(I28/SUM($I$28:$I$35),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="18" customHeight="1">
-      <c r="A29" s="15">
+      <c r="A29" s="6">
         <f>IF(_Pivot!A18="","",_Pivot!A18)</f>
         <v>0</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="7">
         <f>IF(A29="","",_Pivot!B18)</f>
         <v>0</v>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="8">
         <f>IF(A29="","",_Pivot!C18)</f>
         <v>0</v>
       </c>
-      <c r="D29" s="18">
-        <f>IF(A29="","",IFERROR(REPT("█",ROUND(C29*25,0)),""))</f>
-        <v>0</v>
-      </c>
-      <c r="F29" s="3" t="s">
+      <c r="D29" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="20">
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="11">
         <f>IF(F29="","",COUNTIF('Project Data'!$D$3:$D$10000,F29))</f>
         <v>0</v>
       </c>
-      <c r="J29" s="21">
-        <f>IFERROR(I29/SUM($I$28:$I$35),"")</f>
+      <c r="J29" s="12">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="18" customHeight="1">
-      <c r="A30" s="19">
+      <c r="A30" s="10">
         <f>IF(_Pivot!A19="","",_Pivot!A19)</f>
         <v>0</v>
       </c>
-      <c r="B30" s="20">
+      <c r="B30" s="11">
         <f>IF(A30="","",_Pivot!B19)</f>
         <v>0</v>
       </c>
-      <c r="C30" s="21">
+      <c r="C30" s="12">
         <f>IF(A30="","",_Pivot!C19)</f>
         <v>0</v>
       </c>
-      <c r="D30" s="22">
-        <f>IF(A30="","",IFERROR(REPT("█",ROUND(C30*25,0)),""))</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="4" t="s">
+      <c r="D30" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="16">
+      <c r="G30" s="23"/>
+      <c r="H30" s="23"/>
+      <c r="I30" s="7">
         <f>IF(F30="","",COUNTIF('Project Data'!$D$3:$D$10000,F30))</f>
         <v>0</v>
       </c>
-      <c r="J30" s="17">
-        <f>IFERROR(I30/SUM($I$28:$I$35),"")</f>
+      <c r="J30" s="8">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="18" customHeight="1">
-      <c r="A31" s="15">
+      <c r="A31" s="6">
         <f>IF(_Pivot!A20="","",_Pivot!A20)</f>
         <v>0</v>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="7">
         <f>IF(A31="","",_Pivot!B20)</f>
         <v>0</v>
       </c>
-      <c r="C31" s="17">
+      <c r="C31" s="8">
         <f>IF(A31="","",_Pivot!C20)</f>
         <v>0</v>
       </c>
-      <c r="D31" s="18">
-        <f>IF(A31="","",IFERROR(REPT("█",ROUND(C31*25,0)),""))</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="3" t="s">
+      <c r="D31" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="20">
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="11">
         <f>IF(F31="","",COUNTIF('Project Data'!$D$3:$D$10000,F31))</f>
         <v>0</v>
       </c>
-      <c r="J31" s="21">
-        <f>IFERROR(I31/SUM($I$28:$I$35),"")</f>
+      <c r="J31" s="12">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="18" customHeight="1">
-      <c r="A32" s="19">
+      <c r="A32" s="10">
         <f>IF(_Pivot!A21="","",_Pivot!A21)</f>
         <v>0</v>
       </c>
-      <c r="B32" s="20">
+      <c r="B32" s="11">
         <f>IF(A32="","",_Pivot!B21)</f>
         <v>0</v>
       </c>
-      <c r="C32" s="21">
+      <c r="C32" s="12">
         <f>IF(A32="","",_Pivot!C21)</f>
         <v>0</v>
       </c>
-      <c r="D32" s="22">
-        <f>IF(A32="","",IFERROR(REPT("█",ROUND(C32*25,0)),""))</f>
-        <v>0</v>
-      </c>
-      <c r="F32" s="4" t="s">
+      <c r="D32" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="16">
+      <c r="G32" s="23"/>
+      <c r="H32" s="23"/>
+      <c r="I32" s="7">
         <f>IF(F32="","",COUNTIF('Project Data'!$D$3:$D$10000,F32))</f>
         <v>0</v>
       </c>
-      <c r="J32" s="17">
-        <f>IFERROR(I32/SUM($I$28:$I$35),"")</f>
+      <c r="J32" s="8">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="18" customHeight="1">
-      <c r="A33" s="15">
+      <c r="A33" s="6">
         <f>IF(_Pivot!A22="","",_Pivot!A22)</f>
         <v>0</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="7">
         <f>IF(A33="","",_Pivot!B22)</f>
         <v>0</v>
       </c>
-      <c r="C33" s="17">
+      <c r="C33" s="8">
         <f>IF(A33="","",_Pivot!C22)</f>
         <v>0</v>
       </c>
-      <c r="D33" s="18">
-        <f>IF(A33="","",IFERROR(REPT("█",ROUND(C33*25,0)),""))</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="3" t="s">
+      <c r="D33" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="20">
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="11">
         <f>IF(F33="","",COUNTIF('Project Data'!$D$3:$D$10000,F33))</f>
         <v>0</v>
       </c>
-      <c r="J33" s="21">
-        <f>IFERROR(I33/SUM($I$28:$I$35),"")</f>
+      <c r="J33" s="12">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="18" customHeight="1">
-      <c r="A34" s="19">
+      <c r="A34" s="10">
         <f>IF(_Pivot!A23="","",_Pivot!A23)</f>
         <v>0</v>
       </c>
-      <c r="B34" s="20">
+      <c r="B34" s="11">
         <f>IF(A34="","",_Pivot!B23)</f>
         <v>0</v>
       </c>
-      <c r="C34" s="21">
+      <c r="C34" s="12">
         <f>IF(A34="","",_Pivot!C23)</f>
         <v>0</v>
       </c>
-      <c r="D34" s="22">
-        <f>IF(A34="","",IFERROR(REPT("█",ROUND(C34*25,0)),""))</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="4" t="s">
+      <c r="D34" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="16">
+      <c r="G34" s="23"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="7">
         <f>IF(F34="","",COUNTIF('Project Data'!$D$3:$D$10000,F34))</f>
         <v>0</v>
       </c>
-      <c r="J34" s="17">
-        <f>IFERROR(I34/SUM($I$28:$I$35),"")</f>
+      <c r="J34" s="8">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="18" customHeight="1">
-      <c r="A35" s="15">
+      <c r="A35" s="6">
         <f>IF(_Pivot!A24="","",_Pivot!A24)</f>
         <v>0</v>
       </c>
-      <c r="B35" s="16">
+      <c r="B35" s="7">
         <f>IF(A35="","",_Pivot!B24)</f>
         <v>0</v>
       </c>
-      <c r="C35" s="17">
+      <c r="C35" s="8">
         <f>IF(A35="","",_Pivot!C24)</f>
         <v>0</v>
       </c>
-      <c r="D35" s="18">
-        <f>IF(A35="","",IFERROR(REPT("█",ROUND(C35*25,0)),""))</f>
-        <v>0</v>
-      </c>
-      <c r="F35" s="3" t="s">
+      <c r="D35" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="20">
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="11">
         <f>IF(F35="","",COUNTIF('Project Data'!$D$3:$D$10000,F35))</f>
         <v>0</v>
       </c>
-      <c r="J35" s="21">
-        <f>IFERROR(I35/SUM($I$28:$I$35),"")</f>
+      <c r="J35" s="12">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="18" customHeight="1">
-      <c r="A36" s="19">
+      <c r="A36" s="10">
         <f>IF(_Pivot!A25="","",_Pivot!A25)</f>
         <v>0</v>
       </c>
-      <c r="B36" s="20">
+      <c r="B36" s="11">
         <f>IF(A36="","",_Pivot!B25)</f>
         <v>0</v>
       </c>
-      <c r="C36" s="21">
+      <c r="C36" s="12">
         <f>IF(A36="","",_Pivot!C25)</f>
         <v>0</v>
       </c>
-      <c r="D36" s="22">
-        <f>IF(A36="","",IFERROR(REPT("█",ROUND(C36*25,0)),""))</f>
+      <c r="D36" s="13">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="18" customHeight="1">
-      <c r="A37" s="15">
+      <c r="A37" s="6">
         <f>IF(_Pivot!A26="","",_Pivot!A26)</f>
         <v>0</v>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="7">
         <f>IF(A37="","",_Pivot!B26)</f>
         <v>0</v>
       </c>
-      <c r="C37" s="17">
+      <c r="C37" s="8">
         <f>IF(A37="","",_Pivot!C26)</f>
         <v>0</v>
       </c>
-      <c r="D37" s="18">
-        <f>IF(A37="","",IFERROR(REPT("█",ROUND(C37*25,0)),""))</f>
+      <c r="D37" s="9">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="18" customHeight="1">
-      <c r="A38" s="19">
+      <c r="A38" s="10">
         <f>IF(_Pivot!A27="","",_Pivot!A27)</f>
         <v>0</v>
       </c>
-      <c r="B38" s="20">
+      <c r="B38" s="11">
         <f>IF(A38="","",_Pivot!B27)</f>
         <v>0</v>
       </c>
-      <c r="C38" s="21">
+      <c r="C38" s="12">
         <f>IF(A38="","",_Pivot!C27)</f>
         <v>0</v>
       </c>
-      <c r="D38" s="22">
-        <f>IF(A38="","",IFERROR(REPT("█",ROUND(C38*25,0)),""))</f>
+      <c r="D38" s="13">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="18" customHeight="1">
-      <c r="A39" s="15">
+      <c r="A39" s="6">
         <f>IF(_Pivot!A28="","",_Pivot!A28)</f>
         <v>0</v>
       </c>
-      <c r="B39" s="16">
+      <c r="B39" s="7">
         <f>IF(A39="","",_Pivot!B28)</f>
         <v>0</v>
       </c>
-      <c r="C39" s="17">
+      <c r="C39" s="8">
         <f>IF(A39="","",_Pivot!C28)</f>
         <v>0</v>
       </c>
-      <c r="D39" s="18">
-        <f>IF(A39="","",IFERROR(REPT("█",ROUND(C39*25,0)),""))</f>
+      <c r="D39" s="9">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="18" customHeight="1">
-      <c r="A40" s="19">
+      <c r="A40" s="10">
         <f>IF(_Pivot!A29="","",_Pivot!A29)</f>
         <v>0</v>
       </c>
-      <c r="B40" s="20">
+      <c r="B40" s="11">
         <f>IF(A40="","",_Pivot!B29)</f>
         <v>0</v>
       </c>
-      <c r="C40" s="21">
+      <c r="C40" s="12">
         <f>IF(A40="","",_Pivot!C29)</f>
         <v>0</v>
       </c>
-      <c r="D40" s="22">
-        <f>IF(A40="","",IFERROR(REPT("█",ROUND(C40*25,0)),""))</f>
+      <c r="D40" s="13">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="18" customHeight="1">
-      <c r="A41" s="15">
+      <c r="A41" s="6">
         <f>IF(_Pivot!A30="","",_Pivot!A30)</f>
         <v>0</v>
       </c>
-      <c r="B41" s="16">
+      <c r="B41" s="7">
         <f>IF(A41="","",_Pivot!B30)</f>
         <v>0</v>
       </c>
-      <c r="C41" s="17">
+      <c r="C41" s="8">
         <f>IF(A41="","",_Pivot!C30)</f>
         <v>0</v>
       </c>
-      <c r="D41" s="18">
-        <f>IF(A41="","",IFERROR(REPT("█",ROUND(C41*25,0)),""))</f>
+      <c r="D41" s="9">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="18" customHeight="1">
-      <c r="A42" s="19">
+      <c r="A42" s="10">
         <f>IF(_Pivot!A31="","",_Pivot!A31)</f>
         <v>0</v>
       </c>
-      <c r="B42" s="20">
+      <c r="B42" s="11">
         <f>IF(A42="","",_Pivot!B31)</f>
         <v>0</v>
       </c>
-      <c r="C42" s="21">
+      <c r="C42" s="12">
         <f>IF(A42="","",_Pivot!C31)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="22">
-        <f>IF(A42="","",IFERROR(REPT("█",ROUND(C42*25,0)),""))</f>
+      <c r="D42" s="13">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A43" s="23" t="s">
+      <c r="A43" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B43" s="24">
+      <c r="B43" s="15">
         <f>COUNTA('Project Data'!$A$3:$A$10000)</f>
         <v>0</v>
       </c>
-      <c r="C43" s="25">
+      <c r="C43" s="16">
         <f>IFERROR(SUM(C13:C42),"")</f>
         <v>0</v>
       </c>
-      <c r="D43" s="26"/>
+      <c r="D43" s="17"/>
     </row>
     <row r="44" spans="1:10" ht="9.75" customHeight="1"/>
     <row r="45" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A45" s="33" t="s">
+      <c r="A45" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B45" s="33"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="33"/>
+      <c r="B45" s="24"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="24"/>
     </row>
     <row r="46" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A46" s="13" t="s">
+      <c r="A46" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B46" s="14" t="s">
+      <c r="B46" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C46" s="14" t="s">
+      <c r="C46" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D46" s="14" t="s">
+      <c r="D46" s="5" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="18" customHeight="1">
-      <c r="A47" s="15" t="s">
+      <c r="A47" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B47" s="16">
+      <c r="B47" s="7">
         <f>COUNTIF('Project Data'!$F$3:$F$10000,"Male")</f>
         <v>0</v>
       </c>
-      <c r="C47" s="17">
+      <c r="C47" s="8">
         <f>IFERROR(B47/SUM(B47:B50),0)</f>
         <v>0</v>
       </c>
-      <c r="D47" s="18" t="str">
+      <c r="D47" s="9" t="str">
         <f>IFERROR(REPT("█",ROUND(C47*20,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="48" spans="1:10" ht="18" customHeight="1">
-      <c r="A48" s="19" t="s">
+      <c r="A48" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B48" s="20">
+      <c r="B48" s="11">
         <f>COUNTIF('Project Data'!$F$3:$F$10000,"Female")</f>
         <v>0</v>
       </c>
-      <c r="C48" s="21">
+      <c r="C48" s="12">
         <f>IFERROR(B48/SUM(B47:B50),0)</f>
         <v>0</v>
       </c>
-      <c r="D48" s="22" t="str">
+      <c r="D48" s="13" t="str">
         <f>IFERROR(REPT("█",ROUND(C48*20,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:10" ht="18" customHeight="1">
-      <c r="A49" s="15" t="s">
+      <c r="A49" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B49" s="16">
+      <c r="B49" s="7">
         <f>COUNTIF('Project Data'!$F$3:$F$10000,"Non-Binary*")</f>
         <v>0</v>
       </c>
-      <c r="C49" s="17">
+      <c r="C49" s="8">
         <f>IFERROR(B49/SUM(B47:B50),0)</f>
         <v>0</v>
       </c>
-      <c r="D49" s="18" t="str">
+      <c r="D49" s="9" t="str">
         <f>IFERROR(REPT("█",ROUND(C49*20,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="50" spans="1:10" ht="18" customHeight="1">
-      <c r="A50" s="19" t="s">
+      <c r="A50" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B50" s="20">
+      <c r="B50" s="11">
         <f>COUNTIF('Project Data'!$F$3:$F$10000,"Not Specified")</f>
         <v>0</v>
       </c>
-      <c r="C50" s="21">
+      <c r="C50" s="12">
         <f>IFERROR(B50/SUM(B47:B50),0)</f>
         <v>0</v>
       </c>
-      <c r="D50" s="22" t="str">
+      <c r="D50" s="13" t="str">
         <f>IFERROR(REPT("█",ROUND(C50*20,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="51" spans="1:10" ht="9.75" customHeight="1"/>
     <row r="54" spans="1:10" ht="3" customHeight="1">
-      <c r="A54" s="34"/>
-      <c r="B54" s="34"/>
-      <c r="C54" s="34"/>
-      <c r="D54" s="34"/>
-      <c r="E54" s="34"/>
-      <c r="F54" s="34"/>
-      <c r="G54" s="34"/>
-      <c r="H54" s="34"/>
-      <c r="I54" s="34"/>
-      <c r="J54" s="34"/>
+      <c r="A54" s="25"/>
+      <c r="B54" s="25"/>
+      <c r="C54" s="25"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="25"/>
+      <c r="F54" s="25"/>
+      <c r="G54" s="25"/>
+      <c r="H54" s="25"/>
+      <c r="I54" s="25"/>
+      <c r="J54" s="25"/>
     </row>
     <row r="55" spans="1:10" ht="18" customHeight="1">
-      <c r="A55" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
+      <c r="A55" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B55" s="21"/>
+      <c r="C55" s="21"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="21"/>
+      <c r="G55" s="21"/>
+      <c r="H55" s="21"/>
+      <c r="I55" s="21"/>
+      <c r="J55" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="A55:J55"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A54:J54"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="F26:J26"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="A6:B8"/>
-    <mergeCell ref="C6:D8"/>
-    <mergeCell ref="E6:F8"/>
-    <mergeCell ref="G6:H8"/>
-    <mergeCell ref="I6:J8"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
@@ -2644,6 +2612,50 @@
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="I5:J5"/>
+    <mergeCell ref="A6:B8"/>
+    <mergeCell ref="C6:D8"/>
+    <mergeCell ref="E6:F8"/>
+    <mergeCell ref="G6:H8"/>
+    <mergeCell ref="I6:J8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="F26:J26"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="A55:J55"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A54:J54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2660,115 +2672,115 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+    </row>
+    <row r="2" spans="1:6" ht="21.75" customHeight="1">
+      <c r="A2" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A3" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A3" s="27" t="s">
+      <c r="B3" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="28" t="s">
+    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A4" s="18" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A4" s="27" t="s">
+      <c r="B4" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="28" t="s">
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A5" s="18" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A5" s="27" t="s">
+      <c r="B5" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="28" t="s">
+    </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A6" s="20"/>
+      <c r="B6" s="19"/>
+    </row>
+    <row r="7" spans="1:6" ht="21.75" customHeight="1">
+      <c r="A7" s="35" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A6" s="29"/>
-      <c r="B6" s="28"/>
-    </row>
-    <row r="7" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A7" s="30" t="s">
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A8" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A8" s="27" t="s">
+      <c r="B8" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="28" t="s">
+    </row>
+    <row r="9" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A9" s="18" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A9" s="27" t="s">
+      <c r="B9" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="28" t="s">
+    </row>
+    <row r="10" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A10" s="18" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A10" s="27" t="s">
+      <c r="B10" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="B10" s="28" t="s">
+    </row>
+    <row r="11" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A11" s="20"/>
+      <c r="B11" s="19"/>
+    </row>
+    <row r="12" spans="1:6" ht="21.75" customHeight="1">
+      <c r="A12" s="35" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A11" s="29"/>
-      <c r="B11" s="28"/>
-    </row>
-    <row r="12" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A12" s="30" t="s">
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A13" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-    </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A13" s="27" t="s">
+      <c r="B13" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="28" t="s">
+    </row>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A14" s="18" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A14" s="27" t="s">
+      <c r="B14" s="19" t="s">
         <v>85</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>
